--- a/Config/Excel/skill/ability.xlsx
+++ b/Config/Excel/skill/ability.xlsx
@@ -29,9 +29,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>id</t>
+  </si>
+  <si>
+    <t>segmentType</t>
   </si>
   <si>
     <t>segments</t>
@@ -49,7 +52,16 @@
     <t>int[]</t>
   </si>
   <si>
+    <t>段数类型（1、固定列表；2、重复[min,max]）</t>
+  </si>
+  <si>
     <t>120000,120001</t>
+  </si>
+  <si>
+    <t>120000,1,1</t>
+  </si>
+  <si>
+    <t>120000,3,5</t>
   </si>
 </sst>
 </file>
@@ -992,58 +1004,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="22.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="28.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="31.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="D3" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1">
         <v>110000</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>6</v>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1">
+        <v>110001</v>
+      </c>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1">
+        <v>110002</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/skill/ability.xlsx
+++ b/Config/Excel/skill/ability.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\demo\Project001\Config\Excel\skill\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
@@ -29,17 +34,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>segmentType</t>
-  </si>
-  <si>
     <t>segments</t>
   </si>
   <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
     <t>c</t>
   </si>
   <si>
@@ -52,16 +60,19 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>段数类型（1、固定列表；2、重复[min,max]）</t>
+    <t>生效技能段</t>
+  </si>
+  <si>
+    <t>最小次数</t>
+  </si>
+  <si>
+    <t>最大次数</t>
+  </si>
+  <si>
+    <t>120000</t>
   </si>
   <si>
     <t>120000,120001</t>
-  </si>
-  <si>
-    <t>120000,1,1</t>
-  </si>
-  <si>
-    <t>120000,3,5</t>
   </si>
 </sst>
 </file>
@@ -1004,16 +1015,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="3"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
     <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="28.125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="31.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1023,77 +1035,101 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
+      <c r="C3" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>110000</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
+      <c r="E5" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>110001</v>
       </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>9</v>
+      <c r="C6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7" s="1">
         <v>110002</v>
       </c>
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>10</v>
+      <c r="C7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
